--- a/data/trans_dic/P2A_fisi_R-Edad-trans_dic.xlsx
+++ b/data/trans_dic/P2A_fisi_R-Edad-trans_dic.xlsx
@@ -7,7 +7,8 @@
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Variables dicotomizadas" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Porcentajes" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Totales" sheetId="2" state="visible" r:id="rId2"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -526,7 +527,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Hogares con personas con limitación, discapacidad física</t>
+          <t>Hogares con personas con limitación, discapacidad física (tasa de respuesta: 100,0%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -716,37 +717,37 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>0,0; 6,97</t>
+          <t>0,0; 6,16</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>1,16; 6,1</t>
+          <t>1,2; 7,22</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>0,0; 3,11</t>
+          <t>0,0; 3,1</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>1,39; 8,4</t>
+          <t>1,33; 9,2</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>0,0; 4,34</t>
+          <t>0,0; 4,41</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>0,53; 4,54</t>
+          <t>0,0; 4,51</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>0,0; 4,36</t>
+          <t>0,0; 3,94</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -756,22 +757,22 @@
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>0,41; 3,39</t>
+          <t>0,0; 3,35</t>
         </is>
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>0,99; 4,4</t>
+          <t>1,16; 4,67</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>0,0; 2,66</t>
+          <t>0,0; 2,39</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
-          <t>0,85; 4,6</t>
+          <t>0,85; 4,83</t>
         </is>
       </c>
     </row>
@@ -856,62 +857,62 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>0,31; 2,63</t>
+          <t>0,31; 2,96</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>1,33; 6,42</t>
+          <t>1,18; 6,33</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>0,48; 4,31</t>
+          <t>0,61; 5,24</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>1,63; 6,53</t>
+          <t>1,47; 6,31</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>2,16; 7,03</t>
+          <t>2,15; 7,19</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>1,33; 5,49</t>
+          <t>1,35; 5,54</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>0,54; 3,12</t>
+          <t>0,57; 3,28</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>1,89; 7,58</t>
+          <t>1,81; 7,26</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>1,43; 4,14</t>
+          <t>1,4; 4,06</t>
         </is>
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>1,76; 5,14</t>
+          <t>1,75; 4,98</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>0,79; 3,19</t>
+          <t>0,81; 3,11</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
         <is>
-          <t>2,14; 5,69</t>
+          <t>2,14; 5,8</t>
         </is>
       </c>
     </row>
@@ -996,62 +997,62 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>0,0; 4,5</t>
+          <t>0,0; 4,53</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>0,0; 4,8</t>
+          <t>0,0; 4,83</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>1,38; 6,75</t>
+          <t>1,52; 6,43</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>2,36; 7,71</t>
+          <t>2,41; 7,69</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>2,6; 10,19</t>
+          <t>2,65; 10,07</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>0,7; 6,66</t>
+          <t>0,76; 6,67</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>0,45; 4,29</t>
+          <t>0,45; 3,86</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>4,08; 10,25</t>
+          <t>3,64; 10,19</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>1,55; 6,56</t>
+          <t>1,54; 6,1</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>0,98; 4,65</t>
+          <t>0,74; 4,32</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>1,29; 4,44</t>
+          <t>1,25; 4,35</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
         <is>
-          <t>3,77; 7,84</t>
+          <t>3,8; 7,9</t>
         </is>
       </c>
     </row>
@@ -1136,62 +1137,62 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>1,37; 6,36</t>
+          <t>1,5; 6,57</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>1,23; 6,71</t>
+          <t>1,35; 7,24</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>1,68; 8,91</t>
+          <t>1,73; 9,38</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>4,21; 9,71</t>
+          <t>4,27; 9,67</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>1,3; 6,05</t>
+          <t>1,3; 5,9</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>3,76; 10,59</t>
+          <t>3,49; 11,06</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>2,4; 9,93</t>
+          <t>2,17; 9,9</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>5,02; 12,56</t>
+          <t>5,18; 13,5</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>1,79; 5,1</t>
+          <t>1,78; 5,16</t>
         </is>
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>3,05; 7,39</t>
+          <t>3,21; 7,84</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>2,67; 7,92</t>
+          <t>2,81; 7,56</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
-          <t>5,45; 10,39</t>
+          <t>5,46; 10,42</t>
         </is>
       </c>
     </row>
@@ -1276,62 +1277,62 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>0,99; 2,97</t>
+          <t>0,96; 2,93</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>1,75; 4,25</t>
+          <t>1,76; 4,47</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>1,6; 4,16</t>
+          <t>1,55; 4,03</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>3,89; 6,84</t>
+          <t>3,72; 6,61</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>2,4; 4,87</t>
+          <t>2,24; 4,84</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>2,56; 4,99</t>
+          <t>2,48; 5,14</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>1,29; 3,41</t>
+          <t>1,32; 3,33</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>4,56; 8,44</t>
+          <t>4,59; 8,19</t>
         </is>
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>1,95; 3,55</t>
+          <t>1,95; 3,62</t>
         </is>
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>2,29; 4,11</t>
+          <t>2,33; 4,1</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>1,74; 3,3</t>
+          <t>1,72; 3,37</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
         <is>
-          <t>4,6; 6,95</t>
+          <t>4,59; 7,0</t>
         </is>
       </c>
     </row>
@@ -1356,4 +1357,1204 @@
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:N19"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="14" customWidth="1" min="1" max="1"/>
+    <col width="14" customWidth="1" min="2" max="2"/>
+    <col width="14" customWidth="1" min="3" max="3"/>
+    <col width="14" customWidth="1" min="4" max="4"/>
+    <col width="14" customWidth="1" min="5" max="5"/>
+    <col width="14" customWidth="1" min="6" max="6"/>
+    <col width="14" customWidth="1" min="7" max="7"/>
+    <col width="14" customWidth="1" min="8" max="8"/>
+    <col width="14" customWidth="1" min="9" max="9"/>
+    <col width="14" customWidth="1" min="10" max="10"/>
+    <col width="14" customWidth="1" min="11" max="11"/>
+    <col width="14" customWidth="1" min="12" max="12"/>
+    <col width="14" customWidth="1" min="13" max="13"/>
+    <col width="14" customWidth="1" min="14" max="14"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>Hogares con personas con limitación, discapacidad física (tasa de respuesta: 100,0%)</t>
+        </is>
+      </c>
+      <c r="B1" s="2" t="n"/>
+      <c r="C1" s="3" t="inlineStr">
+        <is>
+          <t>Niña</t>
+        </is>
+      </c>
+      <c r="D1" s="3" t="n"/>
+      <c r="E1" s="3" t="n"/>
+      <c r="F1" s="3" t="n"/>
+      <c r="G1" s="3" t="inlineStr">
+        <is>
+          <t>Niño</t>
+        </is>
+      </c>
+      <c r="H1" s="3" t="n"/>
+      <c r="I1" s="3" t="n"/>
+      <c r="J1" s="3" t="n"/>
+      <c r="K1" s="3" t="inlineStr">
+        <is>
+          <t>Total</t>
+        </is>
+      </c>
+      <c r="L1" s="3" t="n"/>
+      <c r="M1" s="3" t="n"/>
+      <c r="N1" s="3" t="n"/>
+    </row>
+    <row r="2">
+      <c r="A2" s="4" t="n"/>
+      <c r="B2" s="2" t="n"/>
+      <c r="C2" s="3" t="inlineStr">
+        <is>
+          <t>2007</t>
+        </is>
+      </c>
+      <c r="D2" s="3" t="inlineStr">
+        <is>
+          <t>2012</t>
+        </is>
+      </c>
+      <c r="E2" s="3" t="inlineStr">
+        <is>
+          <t>2016</t>
+        </is>
+      </c>
+      <c r="F2" s="3" t="inlineStr">
+        <is>
+          <t>2023</t>
+        </is>
+      </c>
+      <c r="G2" s="3" t="inlineStr">
+        <is>
+          <t>2007</t>
+        </is>
+      </c>
+      <c r="H2" s="3" t="inlineStr">
+        <is>
+          <t>2012</t>
+        </is>
+      </c>
+      <c r="I2" s="3" t="inlineStr">
+        <is>
+          <t>2016</t>
+        </is>
+      </c>
+      <c r="J2" s="3" t="inlineStr">
+        <is>
+          <t>2023</t>
+        </is>
+      </c>
+      <c r="K2" s="3" t="inlineStr">
+        <is>
+          <t>2007</t>
+        </is>
+      </c>
+      <c r="L2" s="3" t="inlineStr">
+        <is>
+          <t>2012</t>
+        </is>
+      </c>
+      <c r="M2" s="3" t="inlineStr">
+        <is>
+          <t>2016</t>
+        </is>
+      </c>
+      <c r="N2" s="3" t="inlineStr">
+        <is>
+          <t>2023</t>
+        </is>
+      </c>
+    </row>
+    <row r="3" hidden="1">
+      <c r="A3" s="4" t="n"/>
+      <c r="B3" s="2" t="n"/>
+      <c r="C3" s="2" t="n"/>
+      <c r="D3" s="2" t="n"/>
+      <c r="E3" s="2" t="n"/>
+      <c r="F3" s="2" t="n"/>
+      <c r="G3" s="2" t="n"/>
+      <c r="H3" s="2" t="n"/>
+      <c r="I3" s="2" t="n"/>
+      <c r="J3" s="2" t="n"/>
+      <c r="K3" s="2" t="n"/>
+      <c r="L3" s="2" t="n"/>
+      <c r="M3" s="2" t="n"/>
+      <c r="N3" s="2" t="n"/>
+    </row>
+    <row r="4">
+      <c r="A4" s="1" t="inlineStr">
+        <is>
+          <t>0-2</t>
+        </is>
+      </c>
+      <c r="B4" s="3" t="inlineStr">
+        <is>
+          <t>n</t>
+        </is>
+      </c>
+      <c r="C4" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="D4" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="E4" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="F4" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="G4" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="H4" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="I4" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J4" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K4" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="L4" s="2" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="M4" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="N4" s="2" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="1" t="n"/>
+      <c r="B5" s="3" t="inlineStr">
+        <is>
+          <t>N (estimada)</t>
+        </is>
+      </c>
+      <c r="C5" s="2" t="inlineStr">
+        <is>
+          <t>1399</t>
+        </is>
+      </c>
+      <c r="D5" s="2" t="inlineStr">
+        <is>
+          <t>3126</t>
+        </is>
+      </c>
+      <c r="E5" s="2" t="inlineStr">
+        <is>
+          <t>641</t>
+        </is>
+      </c>
+      <c r="F5" s="2" t="inlineStr">
+        <is>
+          <t>2310</t>
+        </is>
+      </c>
+      <c r="G5" s="2" t="inlineStr">
+        <is>
+          <t>701</t>
+        </is>
+      </c>
+      <c r="H5" s="2" t="inlineStr">
+        <is>
+          <t>1900</t>
+        </is>
+      </c>
+      <c r="I5" s="2" t="inlineStr">
+        <is>
+          <t>715</t>
+        </is>
+      </c>
+      <c r="J5" s="2" t="inlineStr">
+        <is>
+          <t>381</t>
+        </is>
+      </c>
+      <c r="K5" s="2" t="inlineStr">
+        <is>
+          <t>2101</t>
+        </is>
+      </c>
+      <c r="L5" s="2" t="inlineStr">
+        <is>
+          <t>5025</t>
+        </is>
+      </c>
+      <c r="M5" s="2" t="inlineStr">
+        <is>
+          <t>1356</t>
+        </is>
+      </c>
+      <c r="N5" s="2" t="inlineStr">
+        <is>
+          <t>2691</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="1" t="n"/>
+      <c r="B6" s="3" t="inlineStr">
+        <is>
+          <t>IC 95%</t>
+        </is>
+      </c>
+      <c r="C6" s="2" t="inlineStr">
+        <is>
+          <t>0; 4843</t>
+        </is>
+      </c>
+      <c r="D6" s="2" t="inlineStr">
+        <is>
+          <t>1245; 7518</t>
+        </is>
+      </c>
+      <c r="E6" s="2" t="inlineStr">
+        <is>
+          <t>0; 3182</t>
+        </is>
+      </c>
+      <c r="F6" s="2" t="inlineStr">
+        <is>
+          <t>764; 5289</t>
+        </is>
+      </c>
+      <c r="G6" s="2" t="inlineStr">
+        <is>
+          <t>0; 3905</t>
+        </is>
+      </c>
+      <c r="H6" s="2" t="inlineStr">
+        <is>
+          <t>0; 5058</t>
+        </is>
+      </c>
+      <c r="I6" s="2" t="inlineStr">
+        <is>
+          <t>0; 3869</t>
+        </is>
+      </c>
+      <c r="J6" s="2" t="inlineStr">
+        <is>
+          <t>0; 1938</t>
+        </is>
+      </c>
+      <c r="K6" s="2" t="inlineStr">
+        <is>
+          <t>0; 5599</t>
+        </is>
+      </c>
+      <c r="L6" s="2" t="inlineStr">
+        <is>
+          <t>2512; 10102</t>
+        </is>
+      </c>
+      <c r="M6" s="2" t="inlineStr">
+        <is>
+          <t>0; 4809</t>
+        </is>
+      </c>
+      <c r="N6" s="2" t="inlineStr">
+        <is>
+          <t>1006; 5744</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="1" t="inlineStr">
+        <is>
+          <t>3-7</t>
+        </is>
+      </c>
+      <c r="B7" s="3" t="inlineStr">
+        <is>
+          <t>n</t>
+        </is>
+      </c>
+      <c r="C7" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="D7" s="2" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="E7" s="2" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="F7" s="2" t="inlineStr">
+        <is>
+          <t>9</t>
+        </is>
+      </c>
+      <c r="G7" s="2" t="inlineStr">
+        <is>
+          <t>11</t>
+        </is>
+      </c>
+      <c r="H7" s="2" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="I7" s="2" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="J7" s="2" t="inlineStr">
+        <is>
+          <t>9</t>
+        </is>
+      </c>
+      <c r="K7" s="2" t="inlineStr">
+        <is>
+          <t>14</t>
+        </is>
+      </c>
+      <c r="L7" s="2" t="inlineStr">
+        <is>
+          <t>14</t>
+        </is>
+      </c>
+      <c r="M7" s="2" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="N7" s="2" t="inlineStr">
+        <is>
+          <t>18</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="1" t="n"/>
+      <c r="B8" s="3" t="inlineStr">
+        <is>
+          <t>N (estimada)</t>
+        </is>
+      </c>
+      <c r="C8" s="2" t="inlineStr">
+        <is>
+          <t>1826</t>
+        </is>
+      </c>
+      <c r="D8" s="2" t="inlineStr">
+        <is>
+          <t>4885</t>
+        </is>
+      </c>
+      <c r="E8" s="2" t="inlineStr">
+        <is>
+          <t>2943</t>
+        </is>
+      </c>
+      <c r="F8" s="2" t="inlineStr">
+        <is>
+          <t>5385</t>
+        </is>
+      </c>
+      <c r="G8" s="2" t="inlineStr">
+        <is>
+          <t>7463</t>
+        </is>
+      </c>
+      <c r="H8" s="2" t="inlineStr">
+        <is>
+          <t>5707</t>
+        </is>
+      </c>
+      <c r="I8" s="2" t="inlineStr">
+        <is>
+          <t>3131</t>
+        </is>
+      </c>
+      <c r="J8" s="2" t="inlineStr">
+        <is>
+          <t>7156</t>
+        </is>
+      </c>
+      <c r="K8" s="2" t="inlineStr">
+        <is>
+          <t>9289</t>
+        </is>
+      </c>
+      <c r="L8" s="2" t="inlineStr">
+        <is>
+          <t>10592</t>
+        </is>
+      </c>
+      <c r="M8" s="2" t="inlineStr">
+        <is>
+          <t>6074</t>
+        </is>
+      </c>
+      <c r="N8" s="2" t="inlineStr">
+        <is>
+          <t>12541</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="1" t="n"/>
+      <c r="B9" s="3" t="inlineStr">
+        <is>
+          <t>IC 95%</t>
+        </is>
+      </c>
+      <c r="C9" s="2" t="inlineStr">
+        <is>
+          <t>579; 5550</t>
+        </is>
+      </c>
+      <c r="D9" s="2" t="inlineStr">
+        <is>
+          <t>1875; 10081</t>
+        </is>
+      </c>
+      <c r="E9" s="2" t="inlineStr">
+        <is>
+          <t>946; 8187</t>
+        </is>
+      </c>
+      <c r="F9" s="2" t="inlineStr">
+        <is>
+          <t>2338; 10047</t>
+        </is>
+      </c>
+      <c r="G9" s="2" t="inlineStr">
+        <is>
+          <t>4055; 13575</t>
+        </is>
+      </c>
+      <c r="H9" s="2" t="inlineStr">
+        <is>
+          <t>2603; 10707</t>
+        </is>
+      </c>
+      <c r="I9" s="2" t="inlineStr">
+        <is>
+          <t>1194; 6904</t>
+        </is>
+      </c>
+      <c r="J9" s="2" t="inlineStr">
+        <is>
+          <t>3303; 13250</t>
+        </is>
+      </c>
+      <c r="K9" s="2" t="inlineStr">
+        <is>
+          <t>5256; 15266</t>
+        </is>
+      </c>
+      <c r="L9" s="2" t="inlineStr">
+        <is>
+          <t>6166; 17558</t>
+        </is>
+      </c>
+      <c r="M9" s="2" t="inlineStr">
+        <is>
+          <t>2977; 11426</t>
+        </is>
+      </c>
+      <c r="N9" s="2" t="inlineStr">
+        <is>
+          <t>7318; 19821</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="1" t="inlineStr">
+        <is>
+          <t>8-11</t>
+        </is>
+      </c>
+      <c r="B10" s="3" t="inlineStr">
+        <is>
+          <t>n</t>
+        </is>
+      </c>
+      <c r="C10" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="D10" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="E10" s="2" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="F10" s="2" t="inlineStr">
+        <is>
+          <t>11</t>
+        </is>
+      </c>
+      <c r="G10" s="2" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="H10" s="2" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="I10" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="J10" s="2" t="inlineStr">
+        <is>
+          <t>18</t>
+        </is>
+      </c>
+      <c r="K10" s="2" t="inlineStr">
+        <is>
+          <t>9</t>
+        </is>
+      </c>
+      <c r="L10" s="2" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="M10" s="2" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="N10" s="2" t="inlineStr">
+        <is>
+          <t>29</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="1" t="n"/>
+      <c r="B11" s="3" t="inlineStr">
+        <is>
+          <t>N (estimada)</t>
+        </is>
+      </c>
+      <c r="C11" s="2" t="inlineStr">
+        <is>
+          <t>778</t>
+        </is>
+      </c>
+      <c r="D11" s="2" t="inlineStr">
+        <is>
+          <t>1355</t>
+        </is>
+      </c>
+      <c r="E11" s="2" t="inlineStr">
+        <is>
+          <t>4850</t>
+        </is>
+      </c>
+      <c r="F11" s="2" t="inlineStr">
+        <is>
+          <t>7866</t>
+        </is>
+      </c>
+      <c r="G11" s="2" t="inlineStr">
+        <is>
+          <t>5655</t>
+        </is>
+      </c>
+      <c r="H11" s="2" t="inlineStr">
+        <is>
+          <t>2990</t>
+        </is>
+      </c>
+      <c r="I11" s="2" t="inlineStr">
+        <is>
+          <t>2070</t>
+        </is>
+      </c>
+      <c r="J11" s="2" t="inlineStr">
+        <is>
+          <t>13605</t>
+        </is>
+      </c>
+      <c r="K11" s="2" t="inlineStr">
+        <is>
+          <t>6433</t>
+        </is>
+      </c>
+      <c r="L11" s="2" t="inlineStr">
+        <is>
+          <t>4345</t>
+        </is>
+      </c>
+      <c r="M11" s="2" t="inlineStr">
+        <is>
+          <t>6919</t>
+        </is>
+      </c>
+      <c r="N11" s="2" t="inlineStr">
+        <is>
+          <t>21471</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="1" t="n"/>
+      <c r="B12" s="3" t="inlineStr">
+        <is>
+          <t>IC 95%</t>
+        </is>
+      </c>
+      <c r="C12" s="2" t="inlineStr">
+        <is>
+          <t>0; 3914</t>
+        </is>
+      </c>
+      <c r="D12" s="2" t="inlineStr">
+        <is>
+          <t>0; 4737</t>
+        </is>
+      </c>
+      <c r="E12" s="2" t="inlineStr">
+        <is>
+          <t>2192; 9284</t>
+        </is>
+      </c>
+      <c r="F12" s="2" t="inlineStr">
+        <is>
+          <t>4184; 13371</t>
+        </is>
+      </c>
+      <c r="G12" s="2" t="inlineStr">
+        <is>
+          <t>2733; 10402</t>
+        </is>
+      </c>
+      <c r="H12" s="2" t="inlineStr">
+        <is>
+          <t>773; 6787</t>
+        </is>
+      </c>
+      <c r="I12" s="2" t="inlineStr">
+        <is>
+          <t>590; 5108</t>
+        </is>
+      </c>
+      <c r="J12" s="2" t="inlineStr">
+        <is>
+          <t>7728; 21648</t>
+        </is>
+      </c>
+      <c r="K12" s="2" t="inlineStr">
+        <is>
+          <t>2920; 11578</t>
+        </is>
+      </c>
+      <c r="L12" s="2" t="inlineStr">
+        <is>
+          <t>1486; 8638</t>
+        </is>
+      </c>
+      <c r="M12" s="2" t="inlineStr">
+        <is>
+          <t>3450; 12032</t>
+        </is>
+      </c>
+      <c r="N12" s="2" t="inlineStr">
+        <is>
+          <t>14680; 30536</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="1" t="inlineStr">
+        <is>
+          <t>12-15</t>
+        </is>
+      </c>
+      <c r="B13" s="3" t="inlineStr">
+        <is>
+          <t>n</t>
+        </is>
+      </c>
+      <c r="C13" s="2" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="D13" s="2" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="E13" s="2" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="F13" s="2" t="inlineStr">
+        <is>
+          <t>29</t>
+        </is>
+      </c>
+      <c r="G13" s="2" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="H13" s="2" t="inlineStr">
+        <is>
+          <t>13</t>
+        </is>
+      </c>
+      <c r="I13" s="2" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="J13" s="2" t="inlineStr">
+        <is>
+          <t>27</t>
+        </is>
+      </c>
+      <c r="K13" s="2" t="inlineStr">
+        <is>
+          <t>14</t>
+        </is>
+      </c>
+      <c r="L13" s="2" t="inlineStr">
+        <is>
+          <t>19</t>
+        </is>
+      </c>
+      <c r="M13" s="2" t="inlineStr">
+        <is>
+          <t>15</t>
+        </is>
+      </c>
+      <c r="N13" s="2" t="inlineStr">
+        <is>
+          <t>56</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="1" t="n"/>
+      <c r="B14" s="3" t="inlineStr">
+        <is>
+          <t>N (estimada)</t>
+        </is>
+      </c>
+      <c r="C14" s="2" t="inlineStr">
+        <is>
+          <t>4945</t>
+        </is>
+      </c>
+      <c r="D14" s="2" t="inlineStr">
+        <is>
+          <t>3791</t>
+        </is>
+      </c>
+      <c r="E14" s="2" t="inlineStr">
+        <is>
+          <t>5324</t>
+        </is>
+      </c>
+      <c r="F14" s="2" t="inlineStr">
+        <is>
+          <t>18562</t>
+        </is>
+      </c>
+      <c r="G14" s="2" t="inlineStr">
+        <is>
+          <t>4450</t>
+        </is>
+      </c>
+      <c r="H14" s="2" t="inlineStr">
+        <is>
+          <t>8568</t>
+        </is>
+      </c>
+      <c r="I14" s="2" t="inlineStr">
+        <is>
+          <t>6729</t>
+        </is>
+      </c>
+      <c r="J14" s="2" t="inlineStr">
+        <is>
+          <t>24972</t>
+        </is>
+      </c>
+      <c r="K14" s="2" t="inlineStr">
+        <is>
+          <t>9394</t>
+        </is>
+      </c>
+      <c r="L14" s="2" t="inlineStr">
+        <is>
+          <t>12359</t>
+        </is>
+      </c>
+      <c r="M14" s="2" t="inlineStr">
+        <is>
+          <t>12053</t>
+        </is>
+      </c>
+      <c r="N14" s="2" t="inlineStr">
+        <is>
+          <t>43534</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="1" t="n"/>
+      <c r="B15" s="3" t="inlineStr">
+        <is>
+          <t>IC 95%</t>
+        </is>
+      </c>
+      <c r="C15" s="2" t="inlineStr">
+        <is>
+          <t>2261; 9923</t>
+        </is>
+      </c>
+      <c r="D15" s="2" t="inlineStr">
+        <is>
+          <t>1557; 8367</t>
+        </is>
+      </c>
+      <c r="E15" s="2" t="inlineStr">
+        <is>
+          <t>2118; 11457</t>
+        </is>
+      </c>
+      <c r="F15" s="2" t="inlineStr">
+        <is>
+          <t>11751; 26635</t>
+        </is>
+      </c>
+      <c r="G15" s="2" t="inlineStr">
+        <is>
+          <t>1921; 8734</t>
+        </is>
+      </c>
+      <c r="H15" s="2" t="inlineStr">
+        <is>
+          <t>4596; 14572</t>
+        </is>
+      </c>
+      <c r="I15" s="2" t="inlineStr">
+        <is>
+          <t>2827; 12876</t>
+        </is>
+      </c>
+      <c r="J15" s="2" t="inlineStr">
+        <is>
+          <t>15827; 41236</t>
+        </is>
+      </c>
+      <c r="K15" s="2" t="inlineStr">
+        <is>
+          <t>5338; 15449</t>
+        </is>
+      </c>
+      <c r="L15" s="2" t="inlineStr">
+        <is>
+          <t>7939; 19388</t>
+        </is>
+      </c>
+      <c r="M15" s="2" t="inlineStr">
+        <is>
+          <t>7084; 19058</t>
+        </is>
+      </c>
+      <c r="N15" s="2" t="inlineStr">
+        <is>
+          <t>31708; 60549</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" s="1" t="inlineStr">
+        <is>
+          <t>Total</t>
+        </is>
+      </c>
+      <c r="B16" s="3" t="inlineStr">
+        <is>
+          <t>n</t>
+        </is>
+      </c>
+      <c r="C16" s="2" t="inlineStr">
+        <is>
+          <t>13</t>
+        </is>
+      </c>
+      <c r="D16" s="2" t="inlineStr">
+        <is>
+          <t>19</t>
+        </is>
+      </c>
+      <c r="E16" s="2" t="inlineStr">
+        <is>
+          <t>19</t>
+        </is>
+      </c>
+      <c r="F16" s="2" t="inlineStr">
+        <is>
+          <t>54</t>
+        </is>
+      </c>
+      <c r="G16" s="2" t="inlineStr">
+        <is>
+          <t>27</t>
+        </is>
+      </c>
+      <c r="H16" s="2" t="inlineStr">
+        <is>
+          <t>28</t>
+        </is>
+      </c>
+      <c r="I16" s="2" t="inlineStr">
+        <is>
+          <t>18</t>
+        </is>
+      </c>
+      <c r="J16" s="2" t="inlineStr">
+        <is>
+          <t>55</t>
+        </is>
+      </c>
+      <c r="K16" s="2" t="inlineStr">
+        <is>
+          <t>40</t>
+        </is>
+      </c>
+      <c r="L16" s="2" t="inlineStr">
+        <is>
+          <t>47</t>
+        </is>
+      </c>
+      <c r="M16" s="2" t="inlineStr">
+        <is>
+          <t>37</t>
+        </is>
+      </c>
+      <c r="N16" s="2" t="inlineStr">
+        <is>
+          <t>109</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" s="1" t="n"/>
+      <c r="B17" s="3" t="inlineStr">
+        <is>
+          <t>N (estimada)</t>
+        </is>
+      </c>
+      <c r="C17" s="2" t="inlineStr">
+        <is>
+          <t>8948</t>
+        </is>
+      </c>
+      <c r="D17" s="2" t="inlineStr">
+        <is>
+          <t>13156</t>
+        </is>
+      </c>
+      <c r="E17" s="2" t="inlineStr">
+        <is>
+          <t>13758</t>
+        </is>
+      </c>
+      <c r="F17" s="2" t="inlineStr">
+        <is>
+          <t>34124</t>
+        </is>
+      </c>
+      <c r="G17" s="2" t="inlineStr">
+        <is>
+          <t>18269</t>
+        </is>
+      </c>
+      <c r="H17" s="2" t="inlineStr">
+        <is>
+          <t>19165</t>
+        </is>
+      </c>
+      <c r="I17" s="2" t="inlineStr">
+        <is>
+          <t>12645</t>
+        </is>
+      </c>
+      <c r="J17" s="2" t="inlineStr">
+        <is>
+          <t>46113</t>
+        </is>
+      </c>
+      <c r="K17" s="2" t="inlineStr">
+        <is>
+          <t>27217</t>
+        </is>
+      </c>
+      <c r="L17" s="2" t="inlineStr">
+        <is>
+          <t>32322</t>
+        </is>
+      </c>
+      <c r="M17" s="2" t="inlineStr">
+        <is>
+          <t>26402</t>
+        </is>
+      </c>
+      <c r="N17" s="2" t="inlineStr">
+        <is>
+          <t>80237</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" s="1" t="n"/>
+      <c r="B18" s="3" t="inlineStr">
+        <is>
+          <t>IC 95%</t>
+        </is>
+      </c>
+      <c r="C18" s="2" t="inlineStr">
+        <is>
+          <t>4835; 14749</t>
+        </is>
+      </c>
+      <c r="D18" s="2" t="inlineStr">
+        <is>
+          <t>8417; 21328</t>
+        </is>
+      </c>
+      <c r="E18" s="2" t="inlineStr">
+        <is>
+          <t>8157; 21193</t>
+        </is>
+      </c>
+      <c r="F18" s="2" t="inlineStr">
+        <is>
+          <t>24780; 44047</t>
+        </is>
+      </c>
+      <c r="G18" s="2" t="inlineStr">
+        <is>
+          <t>11828; 25565</t>
+        </is>
+      </c>
+      <c r="H18" s="2" t="inlineStr">
+        <is>
+          <t>13359; 27717</t>
+        </is>
+      </c>
+      <c r="I18" s="2" t="inlineStr">
+        <is>
+          <t>7533; 18987</t>
+        </is>
+      </c>
+      <c r="J18" s="2" t="inlineStr">
+        <is>
+          <t>34970; 62420</t>
+        </is>
+      </c>
+      <c r="K18" s="2" t="inlineStr">
+        <is>
+          <t>20139; 37367</t>
+        </is>
+      </c>
+      <c r="L18" s="2" t="inlineStr">
+        <is>
+          <t>23632; 41632</t>
+        </is>
+      </c>
+      <c r="M18" s="2" t="inlineStr">
+        <is>
+          <t>18841; 36896</t>
+        </is>
+      </c>
+      <c r="N18" s="2" t="inlineStr">
+        <is>
+          <t>65572; 100011</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="inlineStr">
+        <is>
+          <t>Fuente: Encuesta Andaluza de Salud (menores)</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <mergeCells count="9">
+    <mergeCell ref="A7:A9"/>
+    <mergeCell ref="A4:A6"/>
+    <mergeCell ref="A16:A18"/>
+    <mergeCell ref="A10:A12"/>
+    <mergeCell ref="A1:B2"/>
+    <mergeCell ref="C1:F1"/>
+    <mergeCell ref="G1:J1"/>
+    <mergeCell ref="K1:N1"/>
+    <mergeCell ref="A13:A15"/>
+  </mergeCells>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
 </file>
--- a/data/trans_dic/P2A_fisi_R-Edad-trans_dic.xlsx
+++ b/data/trans_dic/P2A_fisi_R-Edad-trans_dic.xlsx
@@ -717,62 +717,62 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>0,0; 6,16</t>
+          <t>0,0; 5,76</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>1,2; 7,22</t>
+          <t>1,16; 6,64</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>0,0; 3,1</t>
+          <t>0,0; 2,55</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>1,33; 9,2</t>
+          <t>1,56; 8,56</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>0,0; 4,41</t>
+          <t>0,0; 4,53</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>0,0; 4,51</t>
+          <t>0,53; 4,13</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>0,0; 3,94</t>
+          <t>0,0; 3,3</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>0,0; 3,15</t>
+          <t>0,0; 3,41</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>0,0; 3,35</t>
+          <t>0,41; 3,76</t>
         </is>
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>1,16; 4,67</t>
+          <t>1,15; 4,52</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>0,0; 2,39</t>
+          <t>0,0; 2,07</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
-          <t>0,85; 4,83</t>
+          <t>0,92; 4,83</t>
         </is>
       </c>
     </row>
@@ -857,62 +857,62 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>0,31; 2,96</t>
+          <t>0,31; 2,64</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>1,18; 6,33</t>
+          <t>1,19; 6,46</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>0,61; 5,24</t>
+          <t>0,37; 4,32</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>1,47; 6,31</t>
+          <t>1,64; 6,44</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>2,15; 7,19</t>
+          <t>2,21; 7,25</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>1,35; 5,54</t>
+          <t>1,46; 5,67</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>0,57; 3,28</t>
+          <t>0,57; 3,33</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>1,81; 7,26</t>
+          <t>2,02; 7,33</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>1,4; 4,06</t>
+          <t>1,42; 4,08</t>
         </is>
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>1,75; 4,98</t>
+          <t>1,74; 4,86</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>0,81; 3,11</t>
+          <t>0,81; 3,2</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
         <is>
-          <t>2,14; 5,8</t>
+          <t>2,15; 5,91</t>
         </is>
       </c>
     </row>
@@ -997,62 +997,62 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>0,0; 4,53</t>
+          <t>0,0; 5,13</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>0,0; 4,83</t>
+          <t>0,0; 4,84</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>1,52; 6,43</t>
+          <t>1,4; 7,0</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>2,41; 7,69</t>
+          <t>2,29; 7,65</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>2,65; 10,07</t>
+          <t>2,62; 10,28</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>0,76; 6,67</t>
+          <t>0,83; 7,45</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>0,45; 3,86</t>
+          <t>0,45; 4,25</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>3,64; 10,19</t>
+          <t>3,79; 9,83</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>1,54; 6,1</t>
+          <t>1,76; 6,18</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>0,74; 4,32</t>
+          <t>0,8; 4,73</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>1,25; 4,35</t>
+          <t>1,24; 4,48</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
         <is>
-          <t>3,8; 7,9</t>
+          <t>3,78; 7,91</t>
         </is>
       </c>
     </row>
@@ -1137,62 +1137,62 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>1,5; 6,57</t>
+          <t>1,43; 6,36</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>1,35; 7,24</t>
+          <t>1,23; 7,01</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>1,73; 9,38</t>
+          <t>2,02; 9,04</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>4,27; 9,67</t>
+          <t>4,31; 9,91</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>1,3; 5,9</t>
+          <t>1,28; 6,0</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>3,49; 11,06</t>
+          <t>3,5; 10,59</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>2,17; 9,9</t>
+          <t>2,28; 9,6</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>5,18; 13,5</t>
+          <t>5,09; 13,26</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>1,78; 5,16</t>
+          <t>1,84; 5,07</t>
         </is>
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>3,21; 7,84</t>
+          <t>3,08; 7,63</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>2,81; 7,56</t>
+          <t>2,82; 7,92</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
-          <t>5,46; 10,42</t>
+          <t>5,57; 10,44</t>
         </is>
       </c>
     </row>
@@ -1277,52 +1277,52 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>0,96; 2,93</t>
+          <t>1,0; 2,99</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>1,76; 4,47</t>
+          <t>1,8; 4,31</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>1,55; 4,03</t>
+          <t>1,57; 4,03</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>3,72; 6,61</t>
+          <t>3,96; 6,81</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>2,24; 4,84</t>
+          <t>2,3; 5,04</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>2,48; 5,14</t>
+          <t>2,37; 5,11</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>1,32; 3,33</t>
+          <t>1,28; 3,47</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>4,59; 8,19</t>
+          <t>4,5; 8,13</t>
         </is>
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>1,95; 3,62</t>
+          <t>1,89; 3,56</t>
         </is>
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>2,33; 4,1</t>
+          <t>2,39; 4,15</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
@@ -1332,7 +1332,7 @@
       </c>
       <c r="N13" s="2" t="inlineStr">
         <is>
-          <t>4,59; 7,0</t>
+          <t>4,47; 6,93</t>
         </is>
       </c>
     </row>
@@ -1645,62 +1645,62 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>0; 4843</t>
+          <t>0; 4527</t>
         </is>
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>1245; 7518</t>
+          <t>1208; 6917</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>0; 3182</t>
+          <t>0; 2622</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>764; 5289</t>
+          <t>898; 4923</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
         <is>
-          <t>0; 3905</t>
+          <t>0; 4006</t>
         </is>
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>0; 5058</t>
+          <t>590; 4632</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>0; 3869</t>
+          <t>0; 3241</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
         <is>
-          <t>0; 1938</t>
+          <t>0; 2093</t>
         </is>
       </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>0; 5599</t>
+          <t>683; 6276</t>
         </is>
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>2512; 10102</t>
+          <t>2479; 9763</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>0; 4809</t>
+          <t>0; 4151</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
         <is>
-          <t>1006; 5744</t>
+          <t>1088; 5747</t>
         </is>
       </c>
     </row>
@@ -1853,62 +1853,62 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>579; 5550</t>
+          <t>578; 4946</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>1875; 10081</t>
+          <t>1894; 10299</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>946; 8187</t>
+          <t>573; 6750</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>2338; 10047</t>
+          <t>2620; 10254</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>4055; 13575</t>
+          <t>4179; 13686</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>2603; 10707</t>
+          <t>2821; 10955</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>1194; 6904</t>
+          <t>1190; 7022</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>3303; 13250</t>
+          <t>3680; 13374</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>5256; 15266</t>
+          <t>5337; 15335</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>6166; 17558</t>
+          <t>6123; 17135</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>2977; 11426</t>
+          <t>2985; 11730</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
         <is>
-          <t>7318; 19821</t>
+          <t>7346; 20217</t>
         </is>
       </c>
     </row>
@@ -2061,62 +2061,62 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
-          <t>0; 3914</t>
+          <t>0; 4434</t>
         </is>
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>0; 4737</t>
+          <t>0; 4740</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>2192; 9284</t>
+          <t>2017; 10101</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>4184; 13371</t>
+          <t>3990; 13300</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
         <is>
-          <t>2733; 10402</t>
+          <t>2702; 10614</t>
         </is>
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>773; 6787</t>
+          <t>844; 7588</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>590; 5108</t>
+          <t>594; 5622</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
         <is>
-          <t>7728; 21648</t>
+          <t>8057; 20894</t>
         </is>
       </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>2920; 11578</t>
+          <t>3347; 11725</t>
         </is>
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>1486; 8638</t>
+          <t>1589; 9442</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>3450; 12032</t>
+          <t>3432; 12379</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
         <is>
-          <t>14680; 30536</t>
+          <t>14622; 30558</t>
         </is>
       </c>
     </row>
@@ -2269,62 +2269,62 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>2261; 9923</t>
+          <t>2154; 9608</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>1557; 8367</t>
+          <t>1417; 8096</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>2118; 11457</t>
+          <t>2467; 11039</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>11751; 26635</t>
+          <t>11886; 27293</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>1921; 8734</t>
+          <t>1898; 8891</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>4596; 14572</t>
+          <t>4608; 13953</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>2827; 12876</t>
+          <t>2966; 12475</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>15827; 41236</t>
+          <t>15537; 40506</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>5338; 15449</t>
+          <t>5517; 15181</t>
         </is>
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>7939; 19388</t>
+          <t>7619; 18868</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>7084; 19058</t>
+          <t>7101; 19969</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
         <is>
-          <t>31708; 60549</t>
+          <t>32349; 60675</t>
         </is>
       </c>
     </row>
@@ -2477,62 +2477,62 @@
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
-          <t>4835; 14749</t>
+          <t>5012; 15030</t>
         </is>
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
-          <t>8417; 21328</t>
+          <t>8595; 20541</t>
         </is>
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>8157; 21193</t>
+          <t>8253; 21186</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>24780; 44047</t>
+          <t>26360; 45360</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
         <is>
-          <t>11828; 25565</t>
+          <t>12140; 26620</t>
         </is>
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>13359; 27717</t>
+          <t>12767; 27542</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>7533; 18987</t>
+          <t>7317; 19810</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
         <is>
-          <t>34970; 62420</t>
+          <t>34286; 61958</t>
         </is>
       </c>
       <c r="K18" s="2" t="inlineStr">
         <is>
-          <t>20139; 37367</t>
+          <t>19548; 36688</t>
         </is>
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>23632; 41632</t>
+          <t>24241; 42138</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>18841; 36896</t>
+          <t>18841; 36956</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
         <is>
-          <t>65572; 100011</t>
+          <t>63892; 99037</t>
         </is>
       </c>
     </row>
